--- a/output/ecarts_hommes_femmes/gender_gap.xlsx
+++ b/output/ecarts_hommes_femmes/gender_gap.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Niveau</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -465,13 +465,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>759.73</v>
+        <v>618.89</v>
       </c>
       <c r="D2" t="n">
-        <v>472.73</v>
+        <v>702.16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6222342147868322</v>
+        <v>1.134547334744462</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>401.03</v>
+        <v>431.3</v>
       </c>
       <c r="D3" t="n">
-        <v>419.75</v>
+        <v>419.23</v>
       </c>
       <c r="E3" t="n">
-        <v>1.046679799516246</v>
+        <v>0.9720148388592628</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>375.305</v>
+        <v>370.36</v>
       </c>
       <c r="D4" t="n">
-        <v>367.96</v>
+        <v>368.875</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9804292508759541</v>
+        <v>0.9959903877308565</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>306.88</v>
+        <v>292.31</v>
       </c>
       <c r="D5" t="n">
-        <v>280</v>
+        <v>282.41</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9124087591240876</v>
+        <v>0.9661318463275289</v>
       </c>
     </row>
     <row r="6">
@@ -541,13 +541,13 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>214.67</v>
+        <v>201.255</v>
       </c>
       <c r="D6" t="n">
-        <v>219.085</v>
+        <v>229.56</v>
       </c>
       <c r="E6" t="n">
-        <v>1.020566450831509</v>
+        <v>1.140642468510099</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>157.88</v>
+        <v>169.85</v>
       </c>
       <c r="D7" t="n">
-        <v>166.64</v>
+        <v>154.68</v>
       </c>
       <c r="E7" t="n">
-        <v>1.055485178616671</v>
+        <v>0.9106858993229321</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>127.725</v>
+        <v>132.13</v>
       </c>
       <c r="D8" t="n">
-        <v>120.855</v>
+        <v>120.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9462125660598942</v>
+        <v>0.9122833572996292</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>481.515</v>
+        <v>526.84</v>
       </c>
       <c r="D9" t="n">
-        <v>742.21</v>
+        <v>689.975</v>
       </c>
       <c r="E9" t="n">
-        <v>1.541405771367455</v>
+        <v>1.30964809050186</v>
       </c>
     </row>
     <row r="10">
@@ -617,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>424.09</v>
+        <v>495.71</v>
       </c>
       <c r="D10" t="n">
-        <v>541.39</v>
+        <v>412.635</v>
       </c>
       <c r="E10" t="n">
-        <v>1.276592232780778</v>
+        <v>0.832412095781808</v>
       </c>
     </row>
     <row r="11">
@@ -636,13 +636,13 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>389.805</v>
+        <v>391.39</v>
       </c>
       <c r="D11" t="n">
-        <v>357.3</v>
+        <v>328.57</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9166121522299612</v>
+        <v>0.8394951327320576</v>
       </c>
     </row>
     <row r="12">
@@ -655,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>276.57</v>
+        <v>237.38</v>
       </c>
       <c r="D12" t="n">
-        <v>257.78</v>
+        <v>269.87</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9320605994865675</v>
+        <v>1.136869154941444</v>
       </c>
     </row>
     <row r="13">
@@ -674,13 +674,13 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>202.075</v>
+        <v>216.35</v>
       </c>
       <c r="D13" t="n">
-        <v>216.06</v>
+        <v>186.84</v>
       </c>
       <c r="E13" t="n">
-        <v>1.069206977607324</v>
+        <v>0.8636006470996072</v>
       </c>
     </row>
     <row r="14">
@@ -693,13 +693,13 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>168.3</v>
+        <v>155.47</v>
       </c>
       <c r="D14" t="n">
-        <v>134.935</v>
+        <v>165.26</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8017528223410576</v>
+        <v>1.062970347977102</v>
       </c>
     </row>
     <row r="15">
@@ -712,13 +712,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>109.12</v>
+        <v>145.95</v>
       </c>
       <c r="D15" t="n">
-        <v>128.53</v>
+        <v>124.36</v>
       </c>
       <c r="E15" t="n">
-        <v>1.177877565982405</v>
+        <v>0.852072627612196</v>
       </c>
     </row>
     <row r="16">
@@ -731,13 +731,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>568.97</v>
+        <v>686.59</v>
       </c>
       <c r="D16" t="n">
-        <v>622.54</v>
+        <v>541.8</v>
       </c>
       <c r="E16" t="n">
-        <v>1.094152591525036</v>
+        <v>0.7891172315355597</v>
       </c>
     </row>
     <row r="17">
@@ -750,13 +750,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>425.51</v>
+        <v>495.64</v>
       </c>
       <c r="D17" t="n">
-        <v>414.68</v>
+        <v>485.15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9745481892317455</v>
+        <v>0.9788354450811072</v>
       </c>
     </row>
     <row r="18">
@@ -769,13 +769,13 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>304.98</v>
+        <v>376.33</v>
       </c>
       <c r="D18" t="n">
-        <v>365.73</v>
+        <v>325.61</v>
       </c>
       <c r="E18" t="n">
-        <v>1.199193389730474</v>
+        <v>0.8652246698376426</v>
       </c>
     </row>
     <row r="19">
@@ -788,13 +788,13 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>297.21</v>
+        <v>274.0549999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>277.78</v>
+        <v>257.165</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9346253490797752</v>
+        <v>0.9383700352119103</v>
       </c>
     </row>
     <row r="20">
@@ -807,13 +807,13 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>199.04</v>
+        <v>229.9</v>
       </c>
       <c r="D20" t="n">
-        <v>227.4</v>
+        <v>212.07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.142483922829582</v>
+        <v>0.9224445411048281</v>
       </c>
     </row>
     <row r="21">
@@ -826,13 +826,13 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>168.41</v>
+        <v>178.2</v>
       </c>
       <c r="D21" t="n">
-        <v>163.1</v>
+        <v>161.625</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9684698058310076</v>
+        <v>0.906986531986532</v>
       </c>
     </row>
     <row r="22">
@@ -845,13 +845,13 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>132.775</v>
+        <v>125.01</v>
       </c>
       <c r="D22" t="n">
-        <v>119.055</v>
+        <v>123.45</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8966672942948599</v>
+        <v>0.9875209983201344</v>
       </c>
     </row>
     <row r="23">
@@ -864,13 +864,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>517.9400000000001</v>
+        <v>618.63</v>
       </c>
       <c r="D23" t="n">
-        <v>703.2249999999999</v>
+        <v>802.92</v>
       </c>
       <c r="E23" t="n">
-        <v>1.357734486620072</v>
+        <v>1.297900198826439</v>
       </c>
     </row>
     <row r="24">
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>607.59</v>
+        <v>571.75</v>
       </c>
       <c r="D24" t="n">
-        <v>471.34</v>
+        <v>481.7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7757533863295972</v>
+        <v>0.8425010931351115</v>
       </c>
     </row>
     <row r="25">
@@ -902,13 +902,13 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>411.68</v>
+        <v>470.145</v>
       </c>
       <c r="D25" t="n">
-        <v>472.39</v>
+        <v>553.0699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.147468907889623</v>
+        <v>1.176381754565081</v>
       </c>
     </row>
     <row r="26">
@@ -921,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>392.7</v>
+        <v>365.23</v>
       </c>
       <c r="D26" t="n">
-        <v>395.27</v>
+        <v>373.42</v>
       </c>
       <c r="E26" t="n">
-        <v>1.006544435956201</v>
+        <v>1.022424225830299</v>
       </c>
     </row>
     <row r="27">
@@ -940,13 +940,13 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>274.97</v>
+        <v>315.98</v>
       </c>
       <c r="D27" t="n">
-        <v>298.5549999999999</v>
+        <v>310.225</v>
       </c>
       <c r="E27" t="n">
-        <v>1.085772993417463</v>
+        <v>0.9817868219507564</v>
       </c>
     </row>
     <row r="28">
@@ -959,13 +959,13 @@
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>257.335</v>
+        <v>234.73</v>
       </c>
       <c r="D28" t="n">
-        <v>279.05</v>
+        <v>253.88</v>
       </c>
       <c r="E28" t="n">
-        <v>1.084384168496318</v>
+        <v>1.081583095471393</v>
       </c>
     </row>
     <row r="29">
@@ -978,13 +978,13 @@
         <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>190.35</v>
+        <v>215.39</v>
       </c>
       <c r="D29" t="n">
-        <v>220.67</v>
+        <v>202.535</v>
       </c>
       <c r="E29" t="n">
-        <v>1.159285526661413</v>
+        <v>0.9403175634894843</v>
       </c>
     </row>
     <row r="30">
@@ -997,13 +997,13 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>608.24</v>
+        <v>618.6</v>
       </c>
       <c r="D30" t="n">
-        <v>643.02</v>
+        <v>651.12</v>
       </c>
       <c r="E30" t="n">
-        <v>1.057181375772721</v>
+        <v>1.052570320077594</v>
       </c>
     </row>
     <row r="31">
@@ -1016,13 +1016,13 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>450.14</v>
+        <v>484.205</v>
       </c>
       <c r="D31" t="n">
-        <v>499.025</v>
+        <v>520.34</v>
       </c>
       <c r="E31" t="n">
-        <v>1.10859954680766</v>
+        <v>1.074627482161481</v>
       </c>
     </row>
     <row r="32">
@@ -1035,13 +1035,13 @@
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>367.605</v>
+        <v>358.465</v>
       </c>
       <c r="D32" t="n">
-        <v>329.32</v>
+        <v>348.335</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8958528855701091</v>
+        <v>0.9717406162386846</v>
       </c>
     </row>
     <row r="33">
@@ -1054,13 +1054,13 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>286.89</v>
+        <v>277.5549999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>272.705</v>
+        <v>286.9</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9505559622154833</v>
+        <v>1.033669002540037</v>
       </c>
     </row>
     <row r="34">
@@ -1073,13 +1073,13 @@
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>209.22</v>
+        <v>203.945</v>
       </c>
       <c r="D34" t="n">
-        <v>219.9</v>
+        <v>211.09</v>
       </c>
       <c r="E34" t="n">
-        <v>1.051046745053054</v>
+        <v>1.035033955233029</v>
       </c>
     </row>
     <row r="35">
@@ -1092,13 +1092,13 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>169.73</v>
+        <v>165.66</v>
       </c>
       <c r="D35" t="n">
-        <v>156.89</v>
+        <v>163.405</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9243504389324221</v>
+        <v>0.9863877822045153</v>
       </c>
     </row>
     <row r="36">
@@ -1111,13 +1111,13 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>134.08</v>
+        <v>125.29</v>
       </c>
       <c r="D36" t="n">
-        <v>117.81</v>
+        <v>125.195</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8786545346062052</v>
+        <v>0.9992417591188442</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1130,13 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>628.3</v>
+        <v>629.9000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>643.9400000000001</v>
+        <v>575.375</v>
       </c>
       <c r="E37" t="n">
-        <v>1.024892567244947</v>
+        <v>0.9134386410541354</v>
       </c>
     </row>
     <row r="38">
@@ -1149,13 +1149,13 @@
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>403.6</v>
+        <v>449.12</v>
       </c>
       <c r="D38" t="n">
-        <v>390.75</v>
+        <v>470.93</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9681615460852329</v>
+        <v>1.048561631635198</v>
       </c>
     </row>
     <row r="39">
@@ -1168,13 +1168,13 @@
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>363.96</v>
+        <v>371.095</v>
       </c>
       <c r="D39" t="n">
-        <v>365.245</v>
+        <v>380.25</v>
       </c>
       <c r="E39" t="n">
-        <v>1.003530607759094</v>
+        <v>1.024670232689742</v>
       </c>
     </row>
     <row r="40">
@@ -1187,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>280.475</v>
+        <v>270.13</v>
       </c>
       <c r="D40" t="n">
-        <v>265.31</v>
+        <v>247.95</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9459310098939299</v>
+        <v>0.9178913856291415</v>
       </c>
     </row>
     <row r="41">
@@ -1206,13 +1206,13 @@
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>211.94</v>
+        <v>219.535</v>
       </c>
       <c r="D41" t="n">
-        <v>218.285</v>
+        <v>224.22</v>
       </c>
       <c r="E41" t="n">
-        <v>1.029937718222139</v>
+        <v>1.021340560730635</v>
       </c>
     </row>
     <row r="42">
@@ -1225,13 +1225,13 @@
         <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>157.9</v>
+        <v>161.915</v>
       </c>
       <c r="D42" t="n">
-        <v>157.425</v>
+        <v>159.67</v>
       </c>
       <c r="E42" t="n">
-        <v>0.996991766941102</v>
+        <v>0.9861347003057157</v>
       </c>
     </row>
     <row r="43">
@@ -1244,13 +1244,13 @@
         <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>117.005</v>
+        <v>127.27</v>
       </c>
       <c r="D43" t="n">
-        <v>131.065</v>
+        <v>121</v>
       </c>
       <c r="E43" t="n">
-        <v>1.120165804880133</v>
+        <v>0.9507346585998272</v>
       </c>
     </row>
     <row r="44">
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>821.64</v>
+        <v>753.98</v>
       </c>
       <c r="D44" t="n">
-        <v>815.71</v>
+        <v>681.25</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9927827272284699</v>
+        <v>0.9035385553993475</v>
       </c>
     </row>
     <row r="45">
@@ -1282,13 +1282,13 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>622.63</v>
+        <v>658.48</v>
       </c>
       <c r="D45" t="n">
-        <v>632.14</v>
+        <v>583.91</v>
       </c>
       <c r="E45" t="n">
-        <v>1.015273918699709</v>
+        <v>0.8867543433361681</v>
       </c>
     </row>
     <row r="46">
@@ -1301,13 +1301,13 @@
         <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>463.145</v>
+        <v>512.3</v>
       </c>
       <c r="D46" t="n">
-        <v>496.86</v>
+        <v>521.63</v>
       </c>
       <c r="E46" t="n">
-        <v>1.072795776700601</v>
+        <v>1.018211985164942</v>
       </c>
     </row>
     <row r="47">
@@ -1320,13 +1320,13 @@
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>378.61</v>
+        <v>379.23</v>
       </c>
       <c r="D47" t="n">
-        <v>373.52</v>
+        <v>413.34</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9865560867383323</v>
+        <v>1.089945415710782</v>
       </c>
     </row>
     <row r="48">
@@ -1339,13 +1339,13 @@
         <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>318.73</v>
+        <v>319.55</v>
       </c>
       <c r="D48" t="n">
-        <v>315.65</v>
+        <v>299.785</v>
       </c>
       <c r="E48" t="n">
-        <v>0.990336648574028</v>
+        <v>0.9381473947739006</v>
       </c>
     </row>
     <row r="49">
@@ -1358,13 +1358,13 @@
         <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>241.42</v>
+        <v>256.88</v>
       </c>
       <c r="D49" t="n">
-        <v>250.44</v>
+        <v>250.36</v>
       </c>
       <c r="E49" t="n">
-        <v>1.037362273216801</v>
+        <v>0.974618498909997</v>
       </c>
     </row>
     <row r="50">
@@ -1377,13 +1377,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>197.89</v>
+        <v>205.72</v>
       </c>
       <c r="D50" t="n">
-        <v>197.24</v>
+        <v>200.29</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9967153469098996</v>
+        <v>0.9736048998638926</v>
       </c>
     </row>
     <row r="51">
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>471.78</v>
+        <v>757.23</v>
       </c>
       <c r="D51" t="n">
-        <v>697.9400000000001</v>
+        <v>775.51</v>
       </c>
       <c r="E51" t="n">
-        <v>1.479375980329815</v>
+        <v>1.024140617777954</v>
       </c>
     </row>
     <row r="52">
@@ -1415,13 +1415,13 @@
         <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>455.43</v>
+        <v>404.99</v>
       </c>
       <c r="D52" t="n">
-        <v>439.36</v>
+        <v>378.4</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9647146652614014</v>
+        <v>0.9343440578779723</v>
       </c>
     </row>
     <row r="53">
@@ -1434,13 +1434,13 @@
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>305.565</v>
+        <v>305.23</v>
       </c>
       <c r="D53" t="n">
-        <v>349.005</v>
+        <v>357.69</v>
       </c>
       <c r="E53" t="n">
-        <v>1.142162878601934</v>
+        <v>1.17187039281853</v>
       </c>
     </row>
     <row r="54">
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>294.01</v>
+        <v>245.94</v>
       </c>
       <c r="D54" t="n">
-        <v>283.83</v>
+        <v>244.945</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9653753273698173</v>
+        <v>0.9959542977962105</v>
       </c>
     </row>
     <row r="55">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="C55" t="n">
-        <v>219.665</v>
+        <v>184.35</v>
       </c>
       <c r="D55" t="n">
-        <v>213.74</v>
+        <v>182.375</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9730271094621354</v>
+        <v>0.9892866829400597</v>
       </c>
     </row>
     <row r="56">
@@ -1491,13 +1491,13 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>153.115</v>
+        <v>169.89</v>
       </c>
       <c r="D56" t="n">
-        <v>170.49</v>
+        <v>150.62</v>
       </c>
       <c r="E56" t="n">
-        <v>1.113476798484799</v>
+        <v>0.8865736653128495</v>
       </c>
     </row>
     <row r="57">
@@ -1510,13 +1510,13 @@
         <v>7</v>
       </c>
       <c r="C57" t="n">
-        <v>127.85</v>
+        <v>135.2</v>
       </c>
       <c r="D57" t="n">
-        <v>127.73</v>
+        <v>133.995</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9990614000782168</v>
+        <v>0.991087278106509</v>
       </c>
     </row>
     <row r="58">
@@ -1529,13 +1529,13 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>620.09</v>
+        <v>608.78</v>
       </c>
       <c r="D58" t="n">
-        <v>593.23</v>
+        <v>612.37</v>
       </c>
       <c r="E58" t="n">
-        <v>0.956683707203793</v>
+        <v>1.005897039981603</v>
       </c>
     </row>
     <row r="59">
@@ -1548,13 +1548,13 @@
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>451.27</v>
+        <v>449.49</v>
       </c>
       <c r="D59" t="n">
-        <v>462.95</v>
+        <v>466.76</v>
       </c>
       <c r="E59" t="n">
-        <v>1.025882509362466</v>
+        <v>1.038421321942646</v>
       </c>
     </row>
     <row r="60">
@@ -1567,13 +1567,13 @@
         <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>359.89</v>
+        <v>351.17</v>
       </c>
       <c r="D60" t="n">
-        <v>367.82</v>
+        <v>357.73</v>
       </c>
       <c r="E60" t="n">
-        <v>1.022034510544889</v>
+        <v>1.018680411196856</v>
       </c>
     </row>
     <row r="61">
@@ -1586,13 +1586,13 @@
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>270.865</v>
+        <v>277.32</v>
       </c>
       <c r="D61" t="n">
-        <v>274.27</v>
+        <v>279.505</v>
       </c>
       <c r="E61" t="n">
-        <v>1.012570837871264</v>
+        <v>1.007878984566566</v>
       </c>
     </row>
     <row r="62">
@@ -1605,13 +1605,13 @@
         <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>206.72</v>
+        <v>205.625</v>
       </c>
       <c r="D62" t="n">
-        <v>210.26</v>
+        <v>210.53</v>
       </c>
       <c r="E62" t="n">
-        <v>1.017124613003096</v>
+        <v>1.023854103343465</v>
       </c>
     </row>
     <row r="63">
@@ -1624,13 +1624,13 @@
         <v>6</v>
       </c>
       <c r="C63" t="n">
-        <v>166.35</v>
+        <v>163.96</v>
       </c>
       <c r="D63" t="n">
-        <v>163.03</v>
+        <v>161.845</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9800420799519086</v>
+        <v>0.9871005123200782</v>
       </c>
     </row>
     <row r="64">
@@ -1643,13 +1643,13 @@
         <v>7</v>
       </c>
       <c r="C64" t="n">
-        <v>123.11</v>
+        <v>125.005</v>
       </c>
       <c r="D64" t="n">
-        <v>129.62</v>
+        <v>128.95</v>
       </c>
       <c r="E64" t="n">
-        <v>1.052879538623995</v>
+        <v>1.031558737650494</v>
       </c>
     </row>
     <row r="65">
@@ -1662,13 +1662,13 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>677.405</v>
+        <v>513.8150000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>574.74</v>
+        <v>578.1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8484436932115943</v>
+        <v>1.125113124373559</v>
       </c>
     </row>
     <row r="66">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>475.82</v>
+        <v>489.225</v>
       </c>
       <c r="D66" t="n">
-        <v>486.765</v>
+        <v>509.0650000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>1.023002395863982</v>
+        <v>1.04055393734989</v>
       </c>
     </row>
     <row r="67">
@@ -1700,13 +1700,13 @@
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>347.695</v>
+        <v>366.44</v>
       </c>
       <c r="D67" t="n">
-        <v>355.255</v>
+        <v>369.34</v>
       </c>
       <c r="E67" t="n">
-        <v>1.021743194466415</v>
+        <v>1.007913983189608</v>
       </c>
     </row>
     <row r="68">
@@ -1719,13 +1719,13 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>290.26</v>
+        <v>256.59</v>
       </c>
       <c r="D68" t="n">
-        <v>268.69</v>
+        <v>276.915</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9256873148211948</v>
+        <v>1.079211972407342</v>
       </c>
     </row>
     <row r="69">
@@ -1738,13 +1738,13 @@
         <v>5</v>
       </c>
       <c r="C69" t="n">
-        <v>200.205</v>
+        <v>222.16</v>
       </c>
       <c r="D69" t="n">
-        <v>203.54</v>
+        <v>216.12</v>
       </c>
       <c r="E69" t="n">
-        <v>1.016657925626233</v>
+        <v>0.9728123874684912</v>
       </c>
     </row>
     <row r="70">
@@ -1757,13 +1757,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="n">
-        <v>168.96</v>
+        <v>161.835</v>
       </c>
       <c r="D70" t="n">
-        <v>169.005</v>
+        <v>164.33</v>
       </c>
       <c r="E70" t="n">
-        <v>1.000266335227273</v>
+        <v>1.015416937003738</v>
       </c>
     </row>
     <row r="71">
@@ -1776,13 +1776,13 @@
         <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>114.945</v>
+        <v>136.165</v>
       </c>
       <c r="D71" t="n">
-        <v>126.165</v>
+        <v>120.32</v>
       </c>
       <c r="E71" t="n">
-        <v>1.097611901344121</v>
+        <v>0.8836338266074246</v>
       </c>
     </row>
     <row r="72">
@@ -1794,10 +1794,10 @@
       <c r="B72" t="n">
         <v>1</v>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
-        <v>754.14</v>
-      </c>
+      <c r="C72" t="n">
+        <v>517</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -1810,13 +1810,13 @@
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>338.13</v>
+        <v>381.11</v>
       </c>
       <c r="D73" t="n">
-        <v>352.39</v>
+        <v>579.92</v>
       </c>
       <c r="E73" t="n">
-        <v>1.042173128678319</v>
+        <v>1.521660413004119</v>
       </c>
     </row>
     <row r="74">
@@ -1829,13 +1829,13 @@
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>382.855</v>
+        <v>377.16</v>
       </c>
       <c r="D74" t="n">
-        <v>411.18</v>
+        <v>286.99</v>
       </c>
       <c r="E74" t="n">
-        <v>1.073983623042666</v>
+        <v>0.7609237458903384</v>
       </c>
     </row>
     <row r="75">
@@ -1848,13 +1848,13 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>267.085</v>
+        <v>269.895</v>
       </c>
       <c r="D75" t="n">
-        <v>315.49</v>
+        <v>328.48</v>
       </c>
       <c r="E75" t="n">
-        <v>1.181234438474643</v>
+        <v>1.217065895996591</v>
       </c>
     </row>
     <row r="76">
@@ -1867,13 +1867,13 @@
         <v>5</v>
       </c>
       <c r="C76" t="n">
-        <v>193.03</v>
+        <v>218.02</v>
       </c>
       <c r="D76" t="n">
-        <v>182.68</v>
+        <v>225.295</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9463813914935503</v>
+        <v>1.033368498302908</v>
       </c>
     </row>
     <row r="77">
@@ -1886,13 +1886,13 @@
         <v>6</v>
       </c>
       <c r="C77" t="n">
-        <v>155.74</v>
+        <v>169.825</v>
       </c>
       <c r="D77" t="n">
-        <v>142.915</v>
+        <v>171.98</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9176512135610634</v>
+        <v>1.012689533343147</v>
       </c>
     </row>
     <row r="78">
@@ -1905,13 +1905,13 @@
         <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>134.02</v>
+        <v>126.57</v>
       </c>
       <c r="D78" t="n">
-        <v>114.73</v>
+        <v>126.02</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8560662587673481</v>
+        <v>0.9956545784941141</v>
       </c>
     </row>
     <row r="79">
@@ -1924,13 +1924,13 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>706.2950000000001</v>
+        <v>635.4649999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>721.16</v>
+        <v>773.67</v>
       </c>
       <c r="E79" t="n">
-        <v>1.021046446598093</v>
+        <v>1.217486407591291</v>
       </c>
     </row>
     <row r="80">
@@ -1943,13 +1943,13 @@
         <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>359.095</v>
+        <v>535.96</v>
       </c>
       <c r="D80" t="n">
-        <v>464.71</v>
+        <v>426.45</v>
       </c>
       <c r="E80" t="n">
-        <v>1.29411437084894</v>
+        <v>0.7956750503768937</v>
       </c>
     </row>
     <row r="81">
@@ -1962,13 +1962,13 @@
         <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>375.75</v>
+        <v>328.495</v>
       </c>
       <c r="D81" t="n">
-        <v>375.535</v>
+        <v>414.935</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9994278110445775</v>
+        <v>1.263139469398316</v>
       </c>
     </row>
     <row r="82">
@@ -1981,13 +1981,13 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>257.46</v>
+        <v>280.39</v>
       </c>
       <c r="D82" t="n">
-        <v>282.99</v>
+        <v>253.5</v>
       </c>
       <c r="E82" t="n">
-        <v>1.099161034723841</v>
+        <v>0.9040978636898606</v>
       </c>
     </row>
     <row r="83">
@@ -2000,13 +2000,13 @@
         <v>5</v>
       </c>
       <c r="C83" t="n">
-        <v>202.84</v>
+        <v>212.325</v>
       </c>
       <c r="D83" t="n">
-        <v>215.57</v>
+        <v>202.28</v>
       </c>
       <c r="E83" t="n">
-        <v>1.06275882468941</v>
+        <v>0.9526904509596139</v>
       </c>
     </row>
     <row r="84">
@@ -2019,13 +2019,13 @@
         <v>6</v>
       </c>
       <c r="C84" t="n">
-        <v>154.17</v>
+        <v>159.565</v>
       </c>
       <c r="D84" t="n">
-        <v>145.295</v>
+        <v>157.09</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9424336771096843</v>
+        <v>0.9844890796853947</v>
       </c>
     </row>
     <row r="85">
@@ -2038,13 +2038,13 @@
         <v>7</v>
       </c>
       <c r="C85" t="n">
-        <v>140.945</v>
+        <v>131.8</v>
       </c>
       <c r="D85" t="n">
-        <v>141.95</v>
+        <v>130.185</v>
       </c>
       <c r="E85" t="n">
-        <v>1.007130440952144</v>
+        <v>0.9877465857359635</v>
       </c>
     </row>
     <row r="86">
@@ -2057,13 +2057,13 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>678.76</v>
+        <v>699.72</v>
       </c>
       <c r="D86" t="n">
-        <v>615.39</v>
+        <v>467.39</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9066385762272379</v>
+        <v>0.6679671868747499</v>
       </c>
     </row>
     <row r="87">
@@ -2076,13 +2076,13 @@
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>535.575</v>
+        <v>529.35</v>
       </c>
       <c r="D87" t="n">
-        <v>707.145</v>
+        <v>627.085</v>
       </c>
       <c r="E87" t="n">
-        <v>1.320347290295477</v>
+        <v>1.184632095966752</v>
       </c>
     </row>
     <row r="88">
@@ -2095,13 +2095,13 @@
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>400.78</v>
+        <v>308.825</v>
       </c>
       <c r="D88" t="n">
-        <v>286.385</v>
+        <v>326.66</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7145690902739658</v>
+        <v>1.057751153565935</v>
       </c>
     </row>
     <row r="89">
@@ -2114,13 +2114,13 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>313.22</v>
+        <v>261.82</v>
       </c>
       <c r="D89" t="n">
-        <v>260.255</v>
+        <v>275.095</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8309016027073621</v>
+        <v>1.050702772897411</v>
       </c>
     </row>
     <row r="90">
@@ -2133,13 +2133,13 @@
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>257.385</v>
+        <v>192.265</v>
       </c>
       <c r="D90" t="n">
-        <v>226.22</v>
+        <v>215.14</v>
       </c>
       <c r="E90" t="n">
-        <v>0.8789167977931892</v>
+        <v>1.118976412763633</v>
       </c>
     </row>
     <row r="91">
@@ -2152,13 +2152,13 @@
         <v>6</v>
       </c>
       <c r="C91" t="n">
-        <v>156.815</v>
+        <v>169.6</v>
       </c>
       <c r="D91" t="n">
-        <v>171.86</v>
+        <v>164.19</v>
       </c>
       <c r="E91" t="n">
-        <v>1.095941077065332</v>
+        <v>0.9681014150943394</v>
       </c>
     </row>
     <row r="92">
@@ -2171,13 +2171,13 @@
         <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>114.35</v>
+        <v>141.295</v>
       </c>
       <c r="D92" t="n">
-        <v>122</v>
+        <v>108.4</v>
       </c>
       <c r="E92" t="n">
-        <v>1.066899868823787</v>
+        <v>0.7671892140556991</v>
       </c>
     </row>
   </sheetData>
